--- a/example/pembenahanMfwpJadiExample.xlsx
+++ b/example/pembenahanMfwpJadiExample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Said\PEMBENAHAN RUTIN MFWP 2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Programming\Project 2025\dashmad\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3716A3CB-EBC7-42BD-862C-706C43F208E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77CD2152-1604-449C-9AB3-0EA262C71499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{F0DD1B58-2258-4DC5-B431-C118FD9FB7C8}"/>
+    <workbookView xWindow="28680" yWindow="-330" windowWidth="29040" windowHeight="15840" xr2:uid="{F0DD1B58-2258-4DC5-B431-C118FD9FB7C8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -360,6 +360,72 @@
   <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -367,72 +433,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -758,6 +758,8 @@
     <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="55" customWidth="1"/>
     <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
     <col min="11" max="11" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="23.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.140625" bestFit="1" customWidth="1"/>
@@ -768,698 +770,698 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="4" t="s">
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4" t="s">
+      <c r="L1" s="21"/>
+      <c r="M1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="5" t="s">
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
+      <c r="P1" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="22" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="105" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="6" t="s">
+    <row r="2" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="23"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="O2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="11"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
     </row>
     <row r="4" spans="1:18" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="17">
+      <c r="A4" s="12">
         <v>1</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="12"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="12" t="s">
+      <c r="F4" s="7"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K4" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="L4" s="12" t="s">
+      <c r="L4" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="13" t="s">
+      <c r="M4" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="N4" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="O4" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="P4" s="12" t="s">
+      <c r="N4" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="8"/>
     </row>
     <row r="5" spans="1:18" ht="180" x14ac:dyDescent="0.25">
-      <c r="A5" s="17">
+      <c r="A5" s="12">
         <v>2</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="12" t="s">
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="K5" s="13"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="12" t="s">
+      <c r="K5" s="8"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="Q5" s="20"/>
-      <c r="R5" s="12" t="s">
+      <c r="Q5" s="15"/>
+      <c r="R5" s="7" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="180" x14ac:dyDescent="0.25">
-      <c r="A6" s="17">
+      <c r="A6" s="12">
         <v>4</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="12"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="12" t="s">
+      <c r="F6" s="7"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="12" t="s">
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="12" t="s">
+      <c r="Q6" s="8"/>
+      <c r="R6" s="7" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="180" x14ac:dyDescent="0.25">
-      <c r="A7" s="17">
+      <c r="A7" s="12">
         <v>15</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="20" t="s">
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="21" t="s">
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="12" t="s">
+      <c r="Q7" s="8"/>
+      <c r="R7" s="7" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="180" x14ac:dyDescent="0.25">
-      <c r="A8" s="17">
+      <c r="A8" s="12">
         <v>16</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="20" t="s">
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="12" t="s">
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="12" t="s">
+      <c r="Q8" s="8"/>
+      <c r="R8" s="7" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="17">
+      <c r="A9" s="12">
         <v>17</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12" t="s">
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="K9" s="12" t="s">
+      <c r="K9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="L9" s="12" t="s">
+      <c r="L9" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="12" t="s">
+      <c r="M9" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="N9" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="O9" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="P9" s="23" t="s">
+      <c r="N9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P9" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="12"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
     </row>
     <row r="10" spans="1:18" ht="180" x14ac:dyDescent="0.25">
-      <c r="A10" s="24">
+      <c r="A10" s="19">
         <v>5</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="G10" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="J10" s="12" t="s">
+      <c r="G10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="J10" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="N10" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="O10" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="P10" s="12" t="s">
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P10" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="Q10" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="R10" s="12" t="s">
+      <c r="Q10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="R10" s="7" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="180" x14ac:dyDescent="0.25">
-      <c r="A11" s="24">
+      <c r="A11" s="19">
         <v>6</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="G11" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="J11" s="12" t="s">
+      <c r="G11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="J11" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="N11" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="O11" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="P11" s="12" t="s">
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="O11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P11" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="Q11" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="R11" s="12" t="s">
+      <c r="Q11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="R11" s="7" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="180" x14ac:dyDescent="0.25">
-      <c r="A12" s="24">
+      <c r="A12" s="19">
         <v>7</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="G12" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="I12" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="J12" s="12" t="s">
+      <c r="G12" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="J12" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="K12" s="12"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="N12" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="O12" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="P12" s="12" t="s">
+      <c r="K12" s="7"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="N12" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="O12" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="P12" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q12" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="R12" s="12" t="s">
+      <c r="Q12" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="R12" s="7" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="24">
+      <c r="A13" s="19">
         <v>9</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="G13" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="J13" s="12" t="s">
+      <c r="G13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="J13" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="N13" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="O13" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="P13" s="25" t="s">
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P13" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="Q13" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="R13" s="12" t="s">
+      <c r="Q13" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="R13" s="7" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="180" x14ac:dyDescent="0.25">
-      <c r="A14" s="24">
+      <c r="A14" s="19">
         <v>12</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="G14" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="H14" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="I14" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="J14" s="12" t="s">
+      <c r="G14" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="J14" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="K14" s="12"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="N14" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="O14" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="P14" s="12" t="s">
+      <c r="K14" s="7"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="N14" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="O14" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="P14" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="Q14" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="R14" s="12" t="s">
+      <c r="Q14" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="R14" s="7" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="180" x14ac:dyDescent="0.25">
-      <c r="A15" s="24">
+      <c r="A15" s="19">
         <v>13</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="H15" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="I15" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="J15" s="12" t="s">
+      <c r="G15" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="J15" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="K15" s="12"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="N15" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="O15" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="P15" s="12" t="s">
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P15" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="Q15" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="R15" s="12" t="s">
+      <c r="Q15" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="R15" s="7" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="14"/>
+      <c r="B19" s="9"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="B20" s="14"/>
+      <c r="B20" s="9"/>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="15"/>
-      <c r="B21" s="14" t="s">
+      <c r="A21" s="10"/>
+      <c r="B21" s="9" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="16"/>
-      <c r="B22" s="14" t="s">
+      <c r="A22" s="11"/>
+      <c r="B22" s="9" t="s">
         <v>84</v>
       </c>
     </row>
